--- a/chapters/collection/web_scraping_news.xlsx
+++ b/chapters/collection/web_scraping_news.xlsx
@@ -1886,7 +1886,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Notes for the analyst</t>
+          <t>Notes for the analyst (a realistic teaching dataset written for the book)</t>
         </is>
       </c>
     </row>
@@ -1900,14 +1900,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>The 'frame' is the list of outlets and the time window — choosing it IS a sampling decision (Ch 62–63).</t>
+          <t>The 'frame' is the list of outlets and the time window, and choosing it IS a sampling decision (Ch 63–64).</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>'lean' is operationalized like a survey construct (Ch 68): define indicators, then code; record coder_id + confidence.</t>
+          <t>'lean' is operationalized like a survey construct (Ch 69): define indicators, then code; record coder_id + confidence.</t>
         </is>
       </c>
     </row>
